--- a/results_book.xlsx
+++ b/results_book.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deanmsweeney/Documents/UM-Google Drive/Classes/EECS 598/llm-unlearning/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6BBD73D1-B970-4F4C-BC9F-F5EA6A1A9FC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C89F323A-2FCF-FF4C-BED0-B4DF5E433972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{45056C82-736C-D34B-BDA2-819A8F9EF233}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" activeTab="1" xr2:uid="{45056C82-736C-D34B-BDA2-819A8F9EF233}"/>
   </bookViews>
   <sheets>
     <sheet name="Binary" sheetId="1" r:id="rId1"/>
     <sheet name="Multi" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="21">
   <si>
     <t>k</t>
   </si>
@@ -95,13 +95,19 @@
   <si>
     <t xml:space="preserve">pretrained </t>
   </si>
+  <si>
+    <t>Pretrained</t>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="177" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -141,7 +147,7 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -164,6 +170,1325 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1680" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="Georgia" panose="02040502050405020303" pitchFamily="18" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Fig 1. Validation metrics vs </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" i="1"/>
+              <a:t>k</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t> for multi-class BERT-cased</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> model</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1680" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Georgia" panose="02040502050405020303" pitchFamily="18" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>SS</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="65000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="127000">
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Multi!$C$2:$C$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Multi!$E$2:$E$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0" formatCode="0.000">
+                  <c:v>0.4894514767932483</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.52953586497890248</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.51476793248945119</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.49999999999999933</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.5105485232067507</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-3A7B-7C4C-976C-3D33CFE4961B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>LMS</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="127000">
+                <a:solidFill>
+                  <a:schemeClr val="tx2">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Multi!$C$2:$C$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Multi!$F$2:$F$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0" formatCode="0.000">
+                  <c:v>0.72468354430379678</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.80063291139240444</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.75949367088607578</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.7383966244725737</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.72995780590717263</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-D524-D349-B6A9-E74BA390076A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>ICAT</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="127000">
+                <a:solidFill>
+                  <a:schemeClr val="tx2">
+                    <a:lumMod val="50000"/>
+                    <a:lumOff val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Multi!$C$2:$C$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Multi!$G$2:$G$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0" formatCode="0.000">
+                  <c:v>0.57377518297221974</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.66738210935208953</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.61458181701924819</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.58789071472438514</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.578348452026194</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-D524-D349-B6A9-E74BA390076A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>SS (ref model)</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Multi!$B$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>3000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Multi!$H$3</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0.51259999999999994</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-D524-D349-B6A9-E74BA390076A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="315332287"/>
+        <c:axId val="315327359"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="315332287"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="2.5"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="Georgia" panose="02040502050405020303" pitchFamily="18" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" i="1"/>
+                  <a:t>k</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>*10^-4</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="Georgia" panose="02040502050405020303" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="Georgia" panose="02040502050405020303" pitchFamily="18" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="315327359"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="315327359"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="Georgia" panose="02040502050405020303" pitchFamily="18" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Evaluation Metric (SS, LMS, ICAT) </a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="Georgia" panose="02040502050405020303" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.000" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="Georgia" panose="02040502050405020303" pitchFamily="18" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="315332287"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:legendEntry>
+        <c:idx val="3"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Georgia" panose="02040502050405020303" pitchFamily="18" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="1400">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:latin typeface="Georgia" panose="02040502050405020303" pitchFamily="18" charset="0"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>920750</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>292100</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{439FF6FB-950A-4757-D73A-AF71A50158A3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -483,14 +1808,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{348A6ED3-D573-EA45-B4F9-F140C510FDBB}">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="14.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>6</v>
       </c>
@@ -512,9 +1837,15 @@
       <c r="G1" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="I1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B2">
@@ -524,23 +1855,29 @@
         <v>18</v>
       </c>
       <c r="D2" s="1">
-        <f>(0.615384615384615*B5+0.638418079096045*B6+0.502164502164502*B7+0.625*B8)/SUM(B5:B8)</f>
+        <f>(0.615384615384615*J2+0.638418079096045*J3+0.502164502164502*J4+0.625*J5)/SUM(J2:J5)</f>
         <v>0.56932773109243684</v>
       </c>
       <c r="E2" s="1">
-        <f>(0.85576923076923*B5+0.881355932203389*B6+0.874458874458874*B7+0.8125*B8)/SUM(B5:B8)</f>
+        <f>(0.85576923076923*J2+0.881355932203389*J3+0.874458874458874*J4+0.8125*J5)/SUM(J2:J5)</f>
         <v>0.87289915966386489</v>
       </c>
       <c r="F2" s="1">
-        <f>(0.658284023668638*B5+0.637364741932394*B6+0.870673338205805*B7+0.609375*B8)/SUM(B5:B8)</f>
+        <f>(0.658284023668638*J2+0.637364741932394*J3+0.870673338205805*J4+0.609375*J5)/SUM(J2:J5)</f>
         <v>0.75193249932425188</v>
       </c>
       <c r="G2" s="1">
         <v>0.51608751608751602</v>
       </c>
+      <c r="I2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2">
+        <v>156</v>
+      </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="2"/>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3" s="4"/>
       <c r="B3">
         <v>3000</v>
       </c>
@@ -548,148 +1885,127 @@
         <v>7</v>
       </c>
       <c r="D3" s="1">
-        <f>(0.596153846153846*B5+ 0.598870056497175*B6+0.467532467532467*B7+ 0.5*B8)/SUM(B5:B8)</f>
+        <f>(0.596153846153846*J2+ 0.598870056497175*J3+0.467532467532467*J4+ 0.5*J5)/SUM(J2:J5)</f>
         <v>0.53151260504201647</v>
       </c>
       <c r="E3" s="1">
-        <f>(0.836538461538461*B5 +  0.838983050847457*B6 +  0.844155844155844*B7 + 0.6875*B8)/SUM(B5:B8)</f>
+        <f>(0.836538461538461*J2 +  0.838983050847457*J3 +  0.844155844155844*J4 + 0.6875*J5)/SUM(J2:J5)</f>
         <v>0.8361344537815123</v>
       </c>
       <c r="F3" s="1">
-        <f>(0.675665680473372*B5+0.673082447572536*B6+0.789340529600269*B7+0.6875*B8)/SUM(B5:B8)</f>
+        <f>(0.675665680473372*J2+0.673082447572536*J3+0.789340529600269*J4+0.6875*J5)/SUM(J2:J5)</f>
         <v>0.73026863643406792</v>
       </c>
       <c r="G3" s="1">
         <v>0.50707850707850699</v>
       </c>
+      <c r="I3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J3">
+        <v>531</v>
+      </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="I4" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="I5" t="s">
+        <v>12</v>
+      </c>
+      <c r="J5">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A7" s="3"/>
+      <c r="I7" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="1">
+        <f>(0.623188405797101*J8+ 0.663716814159292*J9+0.592334494773519*J10+0.65*J11)/SUM(J8:J11)</f>
+        <v>0.62458471760797329</v>
+      </c>
+      <c r="E8" s="1">
+        <f>(0.927536231884058*J8+0.913716814159292*J9+0.916376306620209*J10+0.925*J11)/SUM(J8:J11)</f>
+        <v>0.9169435215946844</v>
+      </c>
+      <c r="F8" s="1">
+        <f>(0.699012812434362*J8+0.614535202443417*J9+0.747150020031808*J10+0.6475*J11)/SUM(J8:J11)</f>
+        <v>0.68853637136098345</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0.47951807228915599</v>
+      </c>
+      <c r="I8" t="s">
         <v>9</v>
       </c>
-      <c r="B5">
-        <v>156</v>
+      <c r="J8">
+        <v>207</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A9" s="2"/>
+      <c r="B9">
+        <v>22000</v>
+      </c>
+      <c r="C9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="1">
+        <f>(0.608695652173913*J8+0.570796460176991*J9+0.554006968641115*J10+0.6*J11)/SUM(J8:J11)</f>
+        <v>0.56810631229235875</v>
+      </c>
+      <c r="E9" s="1">
+        <f>(0.847826086956521*J8+0.834070796460177*J9+0.864111498257839*J10+0.775*J11)/SUM(J8:J11)</f>
+        <v>0.8480066445182719</v>
+      </c>
+      <c r="F9" s="1">
+        <f>(0.66351606805293*J8+0.715972276607408*J9+0.770775413080163*J10+0.62*J11)/SUM(J8:J11)</f>
+        <v>0.73289848299490556</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0.472289156626506</v>
+      </c>
+      <c r="I9" t="s">
         <v>10</v>
       </c>
-      <c r="B6">
-        <v>531</v>
+      <c r="J9">
+        <v>678</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="I10" t="s">
         <v>11</v>
       </c>
-      <c r="B7">
-        <v>693</v>
+      <c r="J10">
+        <v>861</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="I11" t="s">
         <v>12</v>
       </c>
-      <c r="B8">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="C10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="1">
-        <f>(0.623188405797101*B13+ 0.663716814159292*B14+0.592334494773519*B15+0.65*B16)/SUM(B13:B16)</f>
-        <v>0.62458471760797329</v>
-      </c>
-      <c r="E10" s="1">
-        <f>(0.927536231884058*B13+0.913716814159292*B14+0.916376306620209*B15+0.925*B16)/SUM(B13:B16)</f>
-        <v>0.9169435215946844</v>
-      </c>
-      <c r="F10" s="1">
-        <f>(0.699012812434362*B13+0.614535202443417*B14+0.747150020031808*B15+0.6475*B16)/SUM(B13:B16)</f>
-        <v>0.68853637136098345</v>
-      </c>
-      <c r="G10" s="1">
-        <v>0.47951807228915599</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="4"/>
-      <c r="B11">
-        <v>22000</v>
-      </c>
-      <c r="C11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" s="1">
-        <f>(0.608695652173913*B13+0.570796460176991*B14+0.554006968641115*B15+0.6*B16)/SUM(B13:B16)</f>
-        <v>0.56810631229235875</v>
-      </c>
-      <c r="E11" s="1">
-        <f>(0.847826086956521*B13+0.834070796460177*B14+0.864111498257839*B15+0.775*B16)/SUM(B13:B16)</f>
-        <v>0.8480066445182719</v>
-      </c>
-      <c r="F11" s="1">
-        <f>(0.66351606805293*B13+0.715972276607408*B14+0.770775413080163*B15+0.62*B16)/SUM(B13:B16)</f>
-        <v>0.73289848299490556</v>
-      </c>
-      <c r="G11" s="1">
-        <v>0.472289156626506</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>11</v>
-      </c>
-      <c r="B15">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B16">
+      <c r="J11">
         <v>60</v>
       </c>
     </row>
@@ -703,9 +2019,337 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98233641-5DE0-A34D-81CD-900C28EC9E68}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:K45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="15.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2">
+        <v>100000</v>
+      </c>
+      <c r="C2">
+        <f>B2/10000</f>
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="1">
+        <f>(0.653846153846153*K2+0.564971751412429*K3+0.382608695652173*K4+0.666666666666666*K5)/SUM(K2:K5)</f>
+        <v>0.4894514767932483</v>
+      </c>
+      <c r="F2" s="1">
+        <f>(0.778846153846153*K2+0.706214689265536*K3+0.728260869565217*K4+0.7*K5)/SUM(K2:K5)</f>
+        <v>0.72468354430379678</v>
+      </c>
+      <c r="G2" s="1">
+        <f>(0.539201183431952*K2+0.614446678796003*K3+0.557277882797731*K4+0.466666666666666*K5)/SUM(K2:K5)</f>
+        <v>0.57377518297221974</v>
+      </c>
+      <c r="J2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A3" s="4"/>
+      <c r="B3">
+        <v>3000</v>
+      </c>
+      <c r="C3">
+        <f t="shared" ref="C3:C6" si="0">B3/10000</f>
+        <v>0.3</v>
+      </c>
+      <c r="D3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3">
+        <f>(0.692307692307692*K2+0.570621468926553*K3+0.443478260869565*K4+0.8*K5)/SUM(K2:K5)</f>
+        <v>0.52953586497890248</v>
+      </c>
+      <c r="F3">
+        <f>(0.85576923076923*K2+0.779661016949152*K3+0.806521739130434*K4+0.766666666666666*K5)/SUM(K2:K5)</f>
+        <v>0.80063291139240444</v>
+      </c>
+      <c r="G3">
+        <f>(0.526627218934911*K2+0.669539404385713*K3+ 0.721069695095669*K4+0.306666666666666*K5)/SUM(K2:K5)</f>
+        <v>0.66738210935208953</v>
+      </c>
+      <c r="H3" s="1">
+        <v>0.51259999999999994</v>
+      </c>
+      <c r="J3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K3">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A4" s="4"/>
+      <c r="B4">
+        <v>10000</v>
+      </c>
+      <c r="C4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4">
+        <f>(0.692307692307692*K2+0.564971751412429*K3+0.417391304347826*K4+0.8*K5)/SUM(K2:K5)</f>
+        <v>0.51476793248945119</v>
+      </c>
+      <c r="F4">
+        <f>(0.788461538461538*K2+0.731638418079096*K3+0.776086956521739*K4+0.733333333333333*K5)/SUM(K2:K5)</f>
+        <v>0.75949367088607578</v>
+      </c>
+      <c r="G4">
+        <f>(0.485207100591716*K2+0.636566759232659*K3+0.647863894139886*K4+0.293333333333333*K5)/SUM(K2:K5)</f>
+        <v>0.61458181701924819</v>
+      </c>
+      <c r="H4" s="1"/>
+      <c r="J4" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A5" s="4"/>
+      <c r="B5">
+        <v>15000</v>
+      </c>
+      <c r="C5">
+        <f t="shared" si="0"/>
+        <v>1.5</v>
+      </c>
+      <c r="D5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5">
+        <f>(0.653846153846153*K2+0.570621468926553*K3+0.395652173913043*K4+0.733333333333333*K5)/SUM(K2:K5)</f>
+        <v>0.49999999999999933</v>
+      </c>
+      <c r="F5">
+        <f>(0.788461538461538*K2+0.720338983050847*K3+0.741304347826087*K4+0.733333333333333*K5)/SUM(K2:K5)</f>
+        <v>0.7383966244725737</v>
+      </c>
+      <c r="G5">
+        <f>(0.54585798816568*K2+0.618596188834626*K3+0.586597353497164*K4+ 0.391111111111111*K5)/SUM(K2:K5)</f>
+        <v>0.58789071472438514</v>
+      </c>
+      <c r="H5" s="1"/>
+      <c r="J5" t="s">
+        <v>12</v>
+      </c>
+      <c r="K5">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A6" s="4"/>
+      <c r="B6">
+        <v>20000</v>
+      </c>
+      <c r="C6">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="D6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6">
+        <f>(0.673076923076923*K2+0.581920903954802*K3+0.404347826086956*K4+0.733333333333333*K5)/SUM(K2:K5)</f>
+        <v>0.5105485232067507</v>
+      </c>
+      <c r="F6">
+        <f>(0.759615384615384*K2+0.714689265536723*K3+0.734782608695652*K4+0.733333333333333*K5)/SUM(K2:K5)</f>
+        <v>0.72995780590717263</v>
+      </c>
+      <c r="G6">
+        <f>(0.496671597633136*K2+0.597593284177599*K3+0.594215500945179*K4+0.391111111111111*K5)/SUM(K2:K5)</f>
+        <v>0.578348452026194</v>
+      </c>
+      <c r="H6" s="1"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>6</v>
+      </c>
+      <c r="B39" t="s">
+        <v>0</v>
+      </c>
+      <c r="D39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E39" t="s">
+        <v>2</v>
+      </c>
+      <c r="F39" t="s">
+        <v>3</v>
+      </c>
+      <c r="G39" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A40" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B40">
+        <v>100000</v>
+      </c>
+      <c r="C40">
+        <v>10</v>
+      </c>
+      <c r="D40" t="s">
+        <v>7</v>
+      </c>
+      <c r="E40">
+        <v>0.52100000000000002</v>
+      </c>
+      <c r="F40">
+        <v>0.66071428571428503</v>
+      </c>
+      <c r="G40">
+        <v>0.54429611378443488</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A41" s="4"/>
+      <c r="B41">
+        <v>3000</v>
+      </c>
+      <c r="C41">
+        <v>0.3</v>
+      </c>
+      <c r="D41" t="s">
+        <v>7</v>
+      </c>
+      <c r="E41">
+        <v>0.52249999999999996</v>
+      </c>
+      <c r="F41">
+        <v>0.76370000000000005</v>
+      </c>
+      <c r="G41">
+        <v>0.64329999999999998</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A42" s="4"/>
+      <c r="B42">
+        <v>10000</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+      <c r="D42" t="s">
+        <v>7</v>
+      </c>
+      <c r="E42">
+        <v>0.53359999999999996</v>
+      </c>
+      <c r="F42">
+        <v>0.70899999999999996</v>
+      </c>
+      <c r="G42">
+        <v>0.61829999999999996</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A43" s="4"/>
+      <c r="B43">
+        <v>15000</v>
+      </c>
+      <c r="C43">
+        <v>1.5</v>
+      </c>
+      <c r="D43" t="s">
+        <v>7</v>
+      </c>
+      <c r="E43">
+        <v>0.52100000000000002</v>
+      </c>
+      <c r="F43">
+        <v>0.67789999999999995</v>
+      </c>
+      <c r="G43">
+        <v>0.58330000000000004</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A44" s="4"/>
+      <c r="B44">
+        <v>20000</v>
+      </c>
+      <c r="C44">
+        <v>2</v>
+      </c>
+      <c r="D44" t="s">
+        <v>7</v>
+      </c>
+      <c r="E44">
+        <v>0.52100840336134424</v>
+      </c>
+      <c r="F44">
+        <v>0.67749999999999999</v>
+      </c>
+      <c r="G44">
+        <v>0.57389999999999997</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A45" s="4"/>
+      <c r="B45" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A40:A45"/>
+    <mergeCell ref="A2:A6"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>